--- a/templates/listino-template.xlsx
+++ b/templates/listino-template.xlsx
@@ -77,19 +77,19 @@
     <t>8001234567890</t>
   </si>
   <si>
-    <t>Gel lubrificante a base acqua 100 ml</t>
+    <t>Shampoo nutriente 250 ml</t>
   </si>
   <si>
     <t>MarcaX</t>
   </si>
   <si>
-    <t>Lubrificanti</t>
+    <t>Cura capelli</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>100 ml</t>
+    <t>250 ml</t>
   </si>
   <si>
     <t>EUR</t>
@@ -122,13 +122,13 @@
     <t>0036000291452</t>
   </si>
   <si>
-    <t>Anello in silicone (confezione da 3)</t>
+    <t>Elastici per capelli (confezione da 3)</t>
   </si>
   <si>
     <t>MarcaY</t>
   </si>
   <si>
-    <t>Accessori</t>
+    <t>Accessori capelli</t>
   </si>
   <si>
     <t>Nero</t>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="I2">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="s">
         <v>26</v>
@@ -696,7 +696,7 @@
         <v>24</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="s">
         <v>26</v>
@@ -731,7 +731,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -770,6 +770,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>